--- a/Projects/CmF_SHG_Women_Entrepreneurs/reports/excel_exports/3_Agency_and_Sourcing_Independence.xlsx
+++ b/Projects/CmF_SHG_Women_Entrepreneurs/reports/excel_exports/3_Agency_and_Sourcing_Independence.xlsx
@@ -506,13 +506,13 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="70" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Empowerment, Agency &amp; Sourcing Independence (All Rajasthan District)</t>
+          <t>Empowerment, Agency &amp; Sourcing Independence (Dausa District)</t>
         </is>
       </c>
     </row>
@@ -546,10 +546,10 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.2142857142857143</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="5">
@@ -562,7 +562,7 @@
         <v>15</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.2678571428571428</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="6">
@@ -575,7 +575,7 @@
         <v>15</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.2678571428571428</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="7">
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="8">
@@ -601,7 +601,7 @@
         <v>21</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.375</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="9">
@@ -653,7 +653,7 @@
         <v>12</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>0.2142857142857143</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="14">
@@ -666,7 +666,7 @@
         <v>17</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>0.3035714285714285</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="15">
@@ -679,7 +679,7 @@
         <v>12</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.2142857142857143</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="16">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>0.1964285714285714</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="19">
